--- a/.migration/saran-url-analysis/Saran-URL-Analysis-Report.xlsx
+++ b/.migration/saran-url-analysis/Saran-URL-Analysis-Report.xlsx
@@ -7,8 +7,9 @@
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
     <sheet name="Templates" sheetId="4" r:id="rId4"/>
     <sheet name="Sections" sheetId="5" r:id="rId5"/>
-    <sheet name="Broken Links" sheetId="6" r:id="rId6"/>
-    <sheet name="Screenshots" sheetId="7" r:id="rId7"/>
+    <sheet name="Feature Prevalence" sheetId="6" r:id="rId6"/>
+    <sheet name="Broken Links" sheetId="7" r:id="rId7"/>
+    <sheet name="Screenshots" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -11905,6 +11906,459 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feature / block / integration</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% of live</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iframe present (any embed)</t>
+        </is>
+      </c>
+      <c r="B2" s="2">
+        <v>375</v>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytics (GA / _ga linker)</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <v>373</v>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Tag Manager</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <v>373</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breadcrumb</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <v>370</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card grid (link cards)</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>257</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">External recipe platform (ahp-recipe.jp)</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <v>236</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tab navigation</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>143</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">News / information list</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>56</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hero carousel / slider</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>44</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data table</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>41</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YouTube video embed</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>28</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accordion / toggle</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>23</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon retail link</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>18</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2B reseller links</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <v>18</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rakuten retail link</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <v>13</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social share buttons</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>10</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scroll-reveal animation</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <v>10</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOHACO retail link</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <v>10</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cookie-consent markup (static)</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <v>9</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campaign microsite link</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>8</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Custom Search (static)</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>7</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Store locator</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <v>7</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI chatbot</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>4</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAQ knowledge base</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <v>4</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Side nav rail</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTML &lt;form&gt; tag</t>
+        </is>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Base: 391 live pages fetched &amp; structurally analyzed)</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
@@ -12516,7 +12970,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
